--- a/data/data_analysis/policy_effectiveness.xlsx
+++ b/data/data_analysis/policy_effectiveness.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natha\PycharmProjects\GCAM-CDR-policy\data\data_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8A1C4F8-CDE2-4787-9998-EEEC2F41CD77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84090143-AFB5-4C78-99D4-BA752A344FFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="2" activeTab="2" xr2:uid="{5B094011-67C9-461D-BBBF-A6D3FE50B4AB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="3" activeTab="5" xr2:uid="{5B094011-67C9-461D-BBBF-A6D3FE50B4AB}"/>
   </bookViews>
   <sheets>
     <sheet name="Low" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Plotting Marginal CostsBenefits" sheetId="5" r:id="rId3"/>
     <sheet name="Marginal C emissions" sheetId="6" r:id="rId4"/>
     <sheet name="Net-Zero Mandate" sheetId="3" r:id="rId5"/>
+    <sheet name="CDR Cost Reduction" sheetId="7" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">High!$A$1:$N$1</definedName>
@@ -25,13 +26,85 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Net-Zero Mandate'!$A$1:$H$30</definedName>
     <definedName name="_xlchart.v1.0" hidden="1">'Net-Zero Mandate'!$A$2:$B$32</definedName>
     <definedName name="_xlchart.v1.1" hidden="1">'Net-Zero Mandate'!$D$1</definedName>
+    <definedName name="_xlchart.v1.10" hidden="1">'CDR Cost Reduction'!$C$1:$C$2</definedName>
+    <definedName name="_xlchart.v1.11" hidden="1">'CDR Cost Reduction'!$C$3:$C$30</definedName>
+    <definedName name="_xlchart.v1.12" hidden="1">'CDR Cost Reduction'!$D$1:$D$2</definedName>
+    <definedName name="_xlchart.v1.13" hidden="1">'CDR Cost Reduction'!$D$3:$D$30</definedName>
+    <definedName name="_xlchart.v1.14" hidden="1">'CDR Cost Reduction'!$E$1:$E$2</definedName>
+    <definedName name="_xlchart.v1.15" hidden="1">'CDR Cost Reduction'!$E$3:$E$30</definedName>
+    <definedName name="_xlchart.v1.16" hidden="1">'CDR Cost Reduction'!$F$1:$F$2</definedName>
+    <definedName name="_xlchart.v1.17" hidden="1">'CDR Cost Reduction'!$F$3:$F$30</definedName>
+    <definedName name="_xlchart.v1.18" hidden="1">'CDR Cost Reduction'!$G$1:$G$2</definedName>
+    <definedName name="_xlchart.v1.19" hidden="1">'CDR Cost Reduction'!$G$3:$G$30</definedName>
     <definedName name="_xlchart.v1.2" hidden="1">'Net-Zero Mandate'!$D$2:$D$32</definedName>
+    <definedName name="_xlchart.v1.20" hidden="1">'CDR Cost Reduction'!$H$1:$H$2</definedName>
+    <definedName name="_xlchart.v1.21" hidden="1">'CDR Cost Reduction'!$H$3:$H$30</definedName>
+    <definedName name="_xlchart.v1.22" hidden="1">'CDR Cost Reduction'!$I$1:$I$2</definedName>
+    <definedName name="_xlchart.v1.23" hidden="1">'CDR Cost Reduction'!$I$3:$I$30</definedName>
+    <definedName name="_xlchart.v1.24" hidden="1">'CDR Cost Reduction'!$J$1:$J$2</definedName>
+    <definedName name="_xlchart.v1.25" hidden="1">'CDR Cost Reduction'!$J$3:$J$30</definedName>
+    <definedName name="_xlchart.v1.26" hidden="1">'CDR Cost Reduction'!$O$10:$P$10</definedName>
+    <definedName name="_xlchart.v1.27" hidden="1">'CDR Cost Reduction'!$O$11</definedName>
+    <definedName name="_xlchart.v1.28" hidden="1">'CDR Cost Reduction'!$O$3:$P$3</definedName>
+    <definedName name="_xlchart.v1.29" hidden="1">'CDR Cost Reduction'!$O$4:$O$10</definedName>
     <definedName name="_xlchart.v1.3" hidden="1">'Net-Zero Mandate'!$F$1</definedName>
+    <definedName name="_xlchart.v1.30" hidden="1">'CDR Cost Reduction'!$O$4:$O$11</definedName>
+    <definedName name="_xlchart.v1.31" hidden="1">'CDR Cost Reduction'!$O$4:$P$4</definedName>
+    <definedName name="_xlchart.v1.32" hidden="1">'CDR Cost Reduction'!$O$5:$P$5</definedName>
+    <definedName name="_xlchart.v1.33" hidden="1">'CDR Cost Reduction'!$O$6:$P$6</definedName>
+    <definedName name="_xlchart.v1.34" hidden="1">'CDR Cost Reduction'!$O$7:$P$7</definedName>
+    <definedName name="_xlchart.v1.35" hidden="1">'CDR Cost Reduction'!$O$8:$P$8</definedName>
+    <definedName name="_xlchart.v1.36" hidden="1">'CDR Cost Reduction'!$O$9:$P$9</definedName>
+    <definedName name="_xlchart.v1.37" hidden="1">'CDR Cost Reduction'!$P$2:$AT$2</definedName>
+    <definedName name="_xlchart.v1.38" hidden="1">'CDR Cost Reduction'!$Q$10:$AT$10</definedName>
+    <definedName name="_xlchart.v1.39" hidden="1">'CDR Cost Reduction'!$Q$1:$AT$2</definedName>
     <definedName name="_xlchart.v1.4" hidden="1">'Net-Zero Mandate'!$F$2:$F$32</definedName>
+    <definedName name="_xlchart.v1.40" hidden="1">'CDR Cost Reduction'!$Q$3:$AT$3</definedName>
+    <definedName name="_xlchart.v1.41" hidden="1">'CDR Cost Reduction'!$Q$4:$AT$4</definedName>
+    <definedName name="_xlchart.v1.42" hidden="1">'CDR Cost Reduction'!$Q$5:$AT$5</definedName>
+    <definedName name="_xlchart.v1.43" hidden="1">'CDR Cost Reduction'!$Q$6:$AT$6</definedName>
+    <definedName name="_xlchart.v1.44" hidden="1">'CDR Cost Reduction'!$Q$7:$AT$7</definedName>
+    <definedName name="_xlchart.v1.45" hidden="1">'CDR Cost Reduction'!$Q$8:$AT$8</definedName>
+    <definedName name="_xlchart.v1.46" hidden="1">'CDR Cost Reduction'!$Q$9:$AT$9</definedName>
+    <definedName name="_xlchart.v1.47" hidden="1">'CDR Cost Reduction'!$B$3:$B$32</definedName>
+    <definedName name="_xlchart.v1.48" hidden="1">'CDR Cost Reduction'!$C$1:$C$2</definedName>
+    <definedName name="_xlchart.v1.49" hidden="1">'CDR Cost Reduction'!$C$3:$C$32</definedName>
     <definedName name="_xlchart.v1.5" hidden="1">'Net-Zero Mandate'!$H$1</definedName>
+    <definedName name="_xlchart.v1.50" hidden="1">'CDR Cost Reduction'!$D$1:$D$2</definedName>
+    <definedName name="_xlchart.v1.51" hidden="1">'CDR Cost Reduction'!$D$3:$D$32</definedName>
+    <definedName name="_xlchart.v1.52" hidden="1">'CDR Cost Reduction'!$E$1:$E$2</definedName>
+    <definedName name="_xlchart.v1.53" hidden="1">'CDR Cost Reduction'!$E$3:$E$32</definedName>
+    <definedName name="_xlchart.v1.54" hidden="1">'CDR Cost Reduction'!$F$1:$F$2</definedName>
+    <definedName name="_xlchart.v1.55" hidden="1">'CDR Cost Reduction'!$F$3:$F$32</definedName>
+    <definedName name="_xlchart.v1.56" hidden="1">'CDR Cost Reduction'!$G$1:$G$2</definedName>
+    <definedName name="_xlchart.v1.57" hidden="1">'CDR Cost Reduction'!$G$3:$G$32</definedName>
+    <definedName name="_xlchart.v1.58" hidden="1">'CDR Cost Reduction'!$H$1:$H$2</definedName>
+    <definedName name="_xlchart.v1.59" hidden="1">'CDR Cost Reduction'!$H$3:$H$32</definedName>
     <definedName name="_xlchart.v1.6" hidden="1">'Net-Zero Mandate'!$H$2:$H$32</definedName>
+    <definedName name="_xlchart.v1.60" hidden="1">'CDR Cost Reduction'!$I$1:$I$2</definedName>
+    <definedName name="_xlchart.v1.61" hidden="1">'CDR Cost Reduction'!$I$3:$I$32</definedName>
+    <definedName name="_xlchart.v1.62" hidden="1">'CDR Cost Reduction'!$J$1:$J$2</definedName>
+    <definedName name="_xlchart.v1.63" hidden="1">'CDR Cost Reduction'!$J$3:$J$32</definedName>
+    <definedName name="_xlchart.v1.64" hidden="1">'CDR Cost Reduction'!$B$3:$B$30</definedName>
+    <definedName name="_xlchart.v1.65" hidden="1">'CDR Cost Reduction'!$C$1:$C$2</definedName>
+    <definedName name="_xlchart.v1.66" hidden="1">'CDR Cost Reduction'!$C$3:$C$30</definedName>
+    <definedName name="_xlchart.v1.67" hidden="1">'CDR Cost Reduction'!$D$1:$D$2</definedName>
+    <definedName name="_xlchart.v1.68" hidden="1">'CDR Cost Reduction'!$D$3:$D$30</definedName>
+    <definedName name="_xlchart.v1.69" hidden="1">'CDR Cost Reduction'!$E$1:$E$2</definedName>
     <definedName name="_xlchart.v1.7" hidden="1">'Net-Zero Mandate'!$I$1</definedName>
+    <definedName name="_xlchart.v1.70" hidden="1">'CDR Cost Reduction'!$E$3:$E$30</definedName>
+    <definedName name="_xlchart.v1.71" hidden="1">'CDR Cost Reduction'!$F$1:$F$2</definedName>
+    <definedName name="_xlchart.v1.72" hidden="1">'CDR Cost Reduction'!$F$3:$F$30</definedName>
+    <definedName name="_xlchart.v1.73" hidden="1">'CDR Cost Reduction'!$G$1:$G$2</definedName>
+    <definedName name="_xlchart.v1.74" hidden="1">'CDR Cost Reduction'!$G$3:$G$30</definedName>
+    <definedName name="_xlchart.v1.75" hidden="1">'CDR Cost Reduction'!$H$1:$H$2</definedName>
+    <definedName name="_xlchart.v1.76" hidden="1">'CDR Cost Reduction'!$H$3:$H$30</definedName>
+    <definedName name="_xlchart.v1.77" hidden="1">'CDR Cost Reduction'!$I$1:$I$2</definedName>
+    <definedName name="_xlchart.v1.78" hidden="1">'CDR Cost Reduction'!$I$3:$I$30</definedName>
+    <definedName name="_xlchart.v1.79" hidden="1">'CDR Cost Reduction'!$J$1:$J$2</definedName>
     <definedName name="_xlchart.v1.8" hidden="1">'Net-Zero Mandate'!$I$2:$I$32</definedName>
+    <definedName name="_xlchart.v1.80" hidden="1">'CDR Cost Reduction'!$J$3:$J$30</definedName>
+    <definedName name="_xlchart.v1.9" hidden="1">'CDR Cost Reduction'!$B$3:$B$30</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -54,7 +127,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="95">
   <si>
     <t>Scenario</t>
   </si>
@@ -337,17 +410,21 @@
   <si>
     <t>Cost of Mitigation in 2050</t>
   </si>
+  <si>
+    <t>2050 Snapshot</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="167" formatCode="0.000%"/>
+    <numFmt numFmtId="170" formatCode="0.0000"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -408,7 +485,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -421,6 +498,10 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -17580,6 +17661,243 @@
 </cx:chartSpace>
 </file>
 
+<file path=xl/charts/chartEx2.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:strDim type="cat">
+        <cx:f>_xlchart.v1.64</cx:f>
+      </cx:strDim>
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.70</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="1">
+      <cx:strDim type="cat">
+        <cx:f>_xlchart.v1.64</cx:f>
+      </cx:strDim>
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.74</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="2">
+      <cx:strDim type="cat">
+        <cx:f>_xlchart.v1.64</cx:f>
+      </cx:strDim>
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.78</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="3">
+      <cx:strDim type="cat">
+        <cx:f>_xlchart.v1.64</cx:f>
+      </cx:strDim>
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.80</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="boxWhisker" uniqueId="{00000002-4C3E-4CD1-BD61-088666F71C44}" formatIdx="2">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.69</cx:f>
+              <cx:v>2% Discount Rate</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{00000004-4C3E-4CD1-BD61-088666F71C44}" formatIdx="4">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.73</cx:f>
+              <cx:v>12% Discount Rate</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="1"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{00000006-4C3E-4CD1-BD61-088666F71C44}" formatIdx="6">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.77</cx:f>
+              <cx:v>20% Discount Rate</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="2"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{00000007-4C3E-4CD1-BD61-088666F71C44}" formatIdx="7">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.79</cx:f>
+              <cx:v>2050 Snapshot</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="3"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0">
+        <cx:catScaling gapWidth="1"/>
+        <cx:title>
+          <cx:tx>
+            <cx:txData>
+              <cx:v>CDR Supply</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:txPr>
+            <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr" rtl="0">
+                <a:defRPr sz="1100">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:defRPr>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+                </a:rPr>
+                <a:t>CDR Supply</a:t>
+              </a:r>
+            </a:p>
+          </cx:txPr>
+        </cx:title>
+        <cx:tickLabels/>
+        <cx:txPr>
+          <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr" rtl="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            </a:endParaRPr>
+          </a:p>
+        </cx:txPr>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling max="100" min="-10"/>
+        <cx:title>
+          <cx:tx>
+            <cx:txData>
+              <cx:v>Reduction in PV of CDR Market (%) to be as Cost-Effective as the 100 Mt Baseline</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:txPr>
+            <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr" rtl="0">
+                <a:defRPr sz="1000">
+                  <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>Reduction in PV of CDR Market (%) to be as Cost-Effective as the 100 Mt Baseline</a:t>
+              </a:r>
+            </a:p>
+          </cx:txPr>
+        </cx:title>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+        <cx:txPr>
+          <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr" rtl="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            </a:endParaRPr>
+          </a:p>
+        </cx:txPr>
+      </cx:axis>
+    </cx:plotArea>
+    <cx:legend pos="t" align="ctr" overlay="0">
+      <cx:txPr>
+        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="900">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+          </a:endParaRPr>
+        </a:p>
+      </cx:txPr>
+    </cx:legend>
+  </cx:chart>
+  <cx:spPr>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+  </cx:spPr>
+</cx:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -17741,6 +18059,46 @@
 </file>
 
 <file path=xl/charts/colors13.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors14.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -20676,6 +21034,521 @@
         <a:noFill/>
       </a:ln>
     </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style14.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="406">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -26423,6 +27296,89 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>380999</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>52386</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>523875</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>190499</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="4" name="Chart 3">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7FAB4FD9-0C41-27D7-4070-958043EFC042}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5581649" y="242886"/>
+              <a:ext cx="2581276" cy="6615113"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This chart isn't available in your version of Excel.
+Editing this shape or saving this workbook into a different file format will permanently break the chart.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -36280,4 +37236,1260 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84803C6B-D47C-4726-9D6A-E26E736B2F56}">
+  <dimension ref="A1:AT35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.42578125" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21" style="15" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="15" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="0" style="15" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="10.85546875" style="15" customWidth="1"/>
+    <col min="11" max="11" width="0" hidden="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="J1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="15">
+        <v>4.9730839656855803</v>
+      </c>
+      <c r="E2" s="14"/>
+      <c r="F2" s="15">
+        <v>1.07999976827834</v>
+      </c>
+      <c r="G2" s="14"/>
+      <c r="H2" s="15">
+        <v>0.44036245439608102</v>
+      </c>
+      <c r="J2" s="14"/>
+      <c r="K2">
+        <v>0.789552850896448</v>
+      </c>
+    </row>
+    <row r="3" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="15">
+        <v>5.0718252254749698</v>
+      </c>
+      <c r="E3">
+        <v>27.6213269143723</v>
+      </c>
+      <c r="F3" s="15">
+        <v>1.10722548717476</v>
+      </c>
+      <c r="G3">
+        <v>38.721957222405898</v>
+      </c>
+      <c r="H3" s="15">
+        <v>0.45309060051576999</v>
+      </c>
+      <c r="I3" s="15">
+        <v>43.944236486980699</v>
+      </c>
+      <c r="J3">
+        <v>10.903288298281099</v>
+      </c>
+      <c r="K3">
+        <v>0.79795728215863404</v>
+      </c>
+    </row>
+    <row r="4" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="15">
+        <v>5.1320980384900201</v>
+      </c>
+      <c r="E4">
+        <v>95.027857894321698</v>
+      </c>
+      <c r="F4" s="15">
+        <v>1.11693365415379</v>
+      </c>
+      <c r="G4">
+        <v>81.341564256248901</v>
+      </c>
+      <c r="H4" s="15">
+        <v>0.45571974620314798</v>
+      </c>
+      <c r="I4" s="15">
+        <v>66.213331230880897</v>
+      </c>
+      <c r="J4">
+        <v>77.537456386603694</v>
+      </c>
+      <c r="K4">
+        <v>0.80479714262603497</v>
+      </c>
+      <c r="O4" s="15"/>
+      <c r="P4" s="15"/>
+      <c r="Q4" s="15"/>
+      <c r="R4" s="15"/>
+      <c r="S4" s="15"/>
+      <c r="T4" s="15"/>
+      <c r="U4" s="15"/>
+      <c r="W4" s="13"/>
+      <c r="X4" s="13"/>
+      <c r="Y4" s="13"/>
+      <c r="Z4" s="13"/>
+      <c r="AB4" s="13"/>
+      <c r="AC4" s="13"/>
+      <c r="AD4" s="15"/>
+      <c r="AE4" s="15"/>
+      <c r="AF4" s="15"/>
+      <c r="AG4" s="15"/>
+      <c r="AH4" s="15"/>
+      <c r="AI4" s="13"/>
+      <c r="AJ4" s="15"/>
+      <c r="AK4" s="13"/>
+      <c r="AL4" s="13"/>
+      <c r="AN4" s="13"/>
+      <c r="AO4" s="13"/>
+      <c r="AP4" s="13"/>
+      <c r="AQ4" s="13"/>
+      <c r="AR4" s="13"/>
+      <c r="AS4" s="15"/>
+      <c r="AT4" s="13"/>
+    </row>
+    <row r="5" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="15">
+        <v>5.0642412818588598</v>
+      </c>
+      <c r="E5">
+        <v>23.2656452481462</v>
+      </c>
+      <c r="F5" s="15">
+        <v>1.10641859927185</v>
+      </c>
+      <c r="G5">
+        <v>34.9056193109856</v>
+      </c>
+      <c r="H5" s="15">
+        <v>0.45405916021112802</v>
+      </c>
+      <c r="I5" s="15">
+        <v>47.160196832255302</v>
+      </c>
+      <c r="J5">
+        <v>10.7774242857275</v>
+      </c>
+      <c r="K5">
+        <v>0.79789188599007999</v>
+      </c>
+      <c r="P5" s="14"/>
+      <c r="W5" s="12"/>
+      <c r="X5" s="12"/>
+      <c r="Y5" s="12"/>
+      <c r="Z5" s="12"/>
+      <c r="AB5" s="12"/>
+      <c r="AC5" s="12"/>
+      <c r="AI5" s="12"/>
+      <c r="AK5" s="12"/>
+      <c r="AL5" s="12"/>
+      <c r="AN5" s="12"/>
+      <c r="AO5" s="12"/>
+      <c r="AP5" s="12"/>
+      <c r="AQ5" s="12"/>
+      <c r="AR5" s="12"/>
+      <c r="AT5" s="12"/>
+    </row>
+    <row r="6" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="O6" s="15"/>
+      <c r="P6" s="15"/>
+      <c r="Q6" s="15"/>
+      <c r="R6" s="15"/>
+      <c r="S6" s="15"/>
+      <c r="T6" s="15"/>
+      <c r="U6" s="15"/>
+      <c r="V6" s="15"/>
+      <c r="W6" s="13"/>
+      <c r="X6" s="13"/>
+      <c r="Y6" s="13"/>
+      <c r="Z6" s="13"/>
+      <c r="AB6" s="13"/>
+      <c r="AC6" s="13"/>
+      <c r="AD6" s="15"/>
+      <c r="AE6" s="15"/>
+      <c r="AF6" s="15"/>
+      <c r="AG6" s="15"/>
+      <c r="AH6" s="15"/>
+      <c r="AI6" s="13"/>
+      <c r="AJ6" s="15"/>
+      <c r="AK6" s="13"/>
+      <c r="AL6" s="13"/>
+      <c r="AM6" s="15"/>
+      <c r="AN6" s="13"/>
+      <c r="AO6" s="13"/>
+      <c r="AP6" s="13"/>
+      <c r="AQ6" s="13"/>
+      <c r="AR6" s="13"/>
+      <c r="AS6" s="15"/>
+      <c r="AT6" s="13"/>
+    </row>
+    <row r="7" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7" s="15">
+        <v>5.0651494080027604</v>
+      </c>
+      <c r="E7">
+        <v>20.740389676832901</v>
+      </c>
+      <c r="F7" s="15">
+        <v>1.1039787764112901</v>
+      </c>
+      <c r="G7">
+        <v>25.5345484743447</v>
+      </c>
+      <c r="H7" s="15">
+        <v>0.452255957782705</v>
+      </c>
+      <c r="I7" s="15">
+        <v>30.623022654211201</v>
+      </c>
+      <c r="J7">
+        <v>12.6101540738449</v>
+      </c>
+      <c r="K7">
+        <v>0.79975092624959898</v>
+      </c>
+      <c r="P7" s="14"/>
+    </row>
+    <row r="8" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>5.0631788067440198</v>
+      </c>
+      <c r="E8">
+        <v>21.4340104562195</v>
+      </c>
+      <c r="F8" s="15">
+        <v>1.1020255007017501</v>
+      </c>
+      <c r="G8">
+        <v>24.6661977907367</v>
+      </c>
+      <c r="H8" s="15">
+        <v>0.44986187328295602</v>
+      </c>
+      <c r="I8" s="15">
+        <v>25.579182243976302</v>
+      </c>
+      <c r="J8">
+        <v>10.690108457101701</v>
+      </c>
+      <c r="K8">
+        <v>0.79773916839968795</v>
+      </c>
+      <c r="O8" s="15"/>
+      <c r="P8" s="15"/>
+      <c r="Q8" s="15"/>
+      <c r="R8" s="15"/>
+      <c r="S8" s="15"/>
+      <c r="T8" s="15"/>
+      <c r="U8" s="15"/>
+      <c r="V8" s="15"/>
+      <c r="W8" s="13"/>
+      <c r="X8" s="13"/>
+      <c r="Y8" s="13"/>
+      <c r="Z8" s="13"/>
+      <c r="AB8" s="13"/>
+      <c r="AC8" s="13"/>
+      <c r="AD8" s="15"/>
+      <c r="AE8" s="15"/>
+      <c r="AF8" s="15"/>
+      <c r="AG8" s="15"/>
+      <c r="AH8" s="15"/>
+      <c r="AI8" s="13"/>
+      <c r="AJ8" s="15"/>
+      <c r="AK8" s="13"/>
+      <c r="AL8" s="13"/>
+      <c r="AM8" s="15"/>
+      <c r="AN8" s="13"/>
+      <c r="AO8" s="13"/>
+      <c r="AP8" s="13"/>
+      <c r="AQ8" s="13"/>
+      <c r="AR8" s="13"/>
+      <c r="AS8" s="15"/>
+      <c r="AT8" s="13"/>
+    </row>
+    <row r="9" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9" s="13">
+        <v>5.0717892080000002</v>
+      </c>
+      <c r="E9" s="12">
+        <v>25.55107559</v>
+      </c>
+      <c r="F9" s="13">
+        <v>1.1068180190000001</v>
+      </c>
+      <c r="G9">
+        <v>32.946601970000003</v>
+      </c>
+      <c r="H9" s="13">
+        <v>0.45191984499999999</v>
+      </c>
+      <c r="I9" s="13">
+        <v>34.183176240000002</v>
+      </c>
+      <c r="J9">
+        <v>6.5878222610000003</v>
+      </c>
+      <c r="K9">
+        <v>0.79431296600000001</v>
+      </c>
+      <c r="O9" s="15"/>
+      <c r="P9" s="15"/>
+      <c r="Q9" s="15"/>
+      <c r="R9" s="15"/>
+      <c r="S9" s="15"/>
+      <c r="T9" s="15"/>
+      <c r="U9" s="15"/>
+      <c r="V9" s="15"/>
+      <c r="W9" s="13"/>
+      <c r="X9" s="13"/>
+      <c r="Y9" s="13"/>
+      <c r="Z9" s="13"/>
+      <c r="AB9" s="13"/>
+      <c r="AC9" s="13"/>
+      <c r="AD9" s="15"/>
+      <c r="AE9" s="15"/>
+      <c r="AF9" s="15"/>
+      <c r="AG9" s="15"/>
+      <c r="AH9" s="15"/>
+      <c r="AI9" s="13"/>
+      <c r="AJ9" s="15"/>
+      <c r="AK9" s="13"/>
+      <c r="AL9" s="13"/>
+      <c r="AM9" s="15"/>
+      <c r="AN9" s="13"/>
+      <c r="AO9" s="13"/>
+      <c r="AP9" s="13"/>
+      <c r="AQ9" s="13"/>
+      <c r="AR9" s="13"/>
+      <c r="AS9" s="15"/>
+      <c r="AT9" s="13"/>
+    </row>
+    <row r="10" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10" s="13">
+        <v>5.0654758229999999</v>
+      </c>
+      <c r="E10" s="12">
+        <v>22.645549119999998</v>
+      </c>
+      <c r="F10" s="13">
+        <v>1.1034140050000001</v>
+      </c>
+      <c r="G10">
+        <v>27.13331105</v>
+      </c>
+      <c r="H10" s="13">
+        <v>0.45035362499999998</v>
+      </c>
+      <c r="I10" s="13">
+        <v>27.845083689999999</v>
+      </c>
+      <c r="J10">
+        <v>9.0841009239999995</v>
+      </c>
+      <c r="K10">
+        <v>0.79640503900000004</v>
+      </c>
+      <c r="P10" s="14"/>
+    </row>
+    <row r="11" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11" s="13">
+        <v>5.0644695789999998</v>
+      </c>
+      <c r="E11" s="12">
+        <v>22.761987189999999</v>
+      </c>
+      <c r="F11" s="13">
+        <v>1.1031711500000001</v>
+      </c>
+      <c r="G11">
+        <v>27.269937800000001</v>
+      </c>
+      <c r="H11" s="13">
+        <v>0.45034164900000001</v>
+      </c>
+      <c r="I11" s="13">
+        <v>28.329187040000001</v>
+      </c>
+      <c r="J11">
+        <v>8.5063978210000002</v>
+      </c>
+      <c r="K11">
+        <v>0.79583269000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12" s="13">
+        <v>5.0645889620000002</v>
+      </c>
+      <c r="E12" s="12">
+        <v>20.58495898</v>
+      </c>
+      <c r="F12" s="13">
+        <v>1.1015991060000001</v>
+      </c>
+      <c r="G12">
+        <v>22.899921719999998</v>
+      </c>
+      <c r="H12" s="13">
+        <v>0.44981676999999998</v>
+      </c>
+      <c r="I12" s="13">
+        <v>24.134127639999999</v>
+      </c>
+      <c r="J12">
+        <v>13.13710908</v>
+      </c>
+      <c r="K12">
+        <v>0.80018215500000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>5.0805945083972404</v>
+      </c>
+      <c r="E13">
+        <v>26.462965375843101</v>
+      </c>
+      <c r="F13">
+        <v>1.11220076960314</v>
+      </c>
+      <c r="G13">
+        <v>38.516546691544299</v>
+      </c>
+      <c r="H13">
+        <v>0.456646404935448</v>
+      </c>
+      <c r="I13">
+        <v>48.6695660201867</v>
+      </c>
+      <c r="J13">
+        <v>9.2006200346008296</v>
+      </c>
+      <c r="K13">
+        <v>0.79650024563104205</v>
+      </c>
+    </row>
+    <row r="14" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14" s="13">
+        <v>5.286561506</v>
+      </c>
+      <c r="E14" s="12">
+        <v>96.268212980000001</v>
+      </c>
+      <c r="F14" s="13">
+        <v>1.1998078539999999</v>
+      </c>
+      <c r="G14">
+        <v>236.62134520000001</v>
+      </c>
+      <c r="H14" s="13">
+        <v>0.510427517</v>
+      </c>
+      <c r="I14" s="13">
+        <v>515.18468129999997</v>
+      </c>
+      <c r="J14">
+        <v>1.9261438340000001</v>
+      </c>
+      <c r="K14">
+        <v>0.79093702099999996</v>
+      </c>
+    </row>
+    <row r="15" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15" s="13">
+        <v>5.0709044319999999</v>
+      </c>
+      <c r="E15" s="12">
+        <v>23.4763971</v>
+      </c>
+      <c r="F15" s="13">
+        <v>1.106159723</v>
+      </c>
+      <c r="G15">
+        <v>29.835672110000001</v>
+      </c>
+      <c r="H15" s="13">
+        <v>0.45247248099999998</v>
+      </c>
+      <c r="I15" s="13">
+        <v>33.564098899999998</v>
+      </c>
+      <c r="J15">
+        <v>10.19934523</v>
+      </c>
+      <c r="K15">
+        <v>0.79736206600000004</v>
+      </c>
+    </row>
+    <row r="16" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16" s="15">
+        <v>5.1811747714499097</v>
+      </c>
+      <c r="E16">
+        <v>20.445962807488002</v>
+      </c>
+      <c r="F16" s="15">
+        <v>1.1344925503854499</v>
+      </c>
+      <c r="G16">
+        <v>33.296985967255303</v>
+      </c>
+      <c r="H16" s="15">
+        <v>0.46492193565777301</v>
+      </c>
+      <c r="I16" s="15">
+        <v>45.482460902694598</v>
+      </c>
+      <c r="J16">
+        <v>4.2929028443568198</v>
+      </c>
+      <c r="K16">
+        <v>0.80197587970054995</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>2</v>
+      </c>
+      <c r="B17" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17" s="15">
+        <v>5.2414073348661097</v>
+      </c>
+      <c r="E17">
+        <v>62.001488876347999</v>
+      </c>
+      <c r="F17" s="15">
+        <v>1.14596942451646</v>
+      </c>
+      <c r="G17">
+        <v>73.808838074483504</v>
+      </c>
+      <c r="H17" s="15">
+        <v>0.468332151856236</v>
+      </c>
+      <c r="I17" s="15">
+        <v>75.181945791756903</v>
+      </c>
+      <c r="J17">
+        <v>9.0041609658021802</v>
+      </c>
+      <c r="K17">
+        <v>0.79733908932737696</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18" s="15">
+        <v>5.1754846755394803</v>
+      </c>
+      <c r="E18">
+        <v>18.358116920014702</v>
+      </c>
+      <c r="F18" s="15">
+        <v>1.1343808780025699</v>
+      </c>
+      <c r="G18">
+        <v>29.945423567779098</v>
+      </c>
+      <c r="H18" s="15">
+        <v>0.46670096287577201</v>
+      </c>
+      <c r="I18" s="15">
+        <v>44.9719994818999</v>
+      </c>
+      <c r="J18">
+        <v>4.5299326625634597</v>
+      </c>
+      <c r="K18">
+        <v>0.80271254928786895</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>78</v>
+      </c>
+      <c r="B20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20" s="15">
+        <v>5.2054763144523601</v>
+      </c>
+      <c r="E20">
+        <v>19.569169104060201</v>
+      </c>
+      <c r="F20" s="15">
+        <v>1.1315450470849799</v>
+      </c>
+      <c r="G20">
+        <v>24.7795344738106</v>
+      </c>
+      <c r="H20" s="15">
+        <v>0.46163241164495999</v>
+      </c>
+      <c r="I20" s="15">
+        <v>29.445243255130102</v>
+      </c>
+      <c r="J20">
+        <v>8.4504572715756492</v>
+      </c>
+      <c r="K20">
+        <v>0.81490689546323802</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21" s="13">
+        <v>5.2021279229999999</v>
+      </c>
+      <c r="E21" s="12">
+        <v>19.347934510000002</v>
+      </c>
+      <c r="F21" s="13">
+        <v>1.1332403150000001</v>
+      </c>
+      <c r="G21">
+        <v>25.7031423</v>
+      </c>
+      <c r="H21" s="13">
+        <v>0.46383227999999999</v>
+      </c>
+      <c r="I21" s="13">
+        <v>32.714646649999999</v>
+      </c>
+      <c r="J21">
+        <v>7.9367565070000001</v>
+      </c>
+      <c r="K21">
+        <v>0.81326671699999997</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22" s="15">
+        <v>5.1720279541023402</v>
+      </c>
+      <c r="E22">
+        <v>17.426437752642599</v>
+      </c>
+      <c r="F22" s="15">
+        <v>1.1272007430390301</v>
+      </c>
+      <c r="G22">
+        <v>23.678534872133099</v>
+      </c>
+      <c r="H22" s="15">
+        <v>0.46032657024823997</v>
+      </c>
+      <c r="I22" s="15">
+        <v>28.918131262142602</v>
+      </c>
+      <c r="J22">
+        <v>4.5221188649834598</v>
+      </c>
+      <c r="K22">
+        <v>0.80266837264658997</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23" s="13">
+        <v>5.1380938110000001</v>
+      </c>
+      <c r="E23" s="12">
+        <v>15.27203439</v>
+      </c>
+      <c r="F23" s="13">
+        <v>1.1249029639999999</v>
+      </c>
+      <c r="G23">
+        <v>24.125784410000001</v>
+      </c>
+      <c r="H23" s="13">
+        <v>0.46008382799999997</v>
+      </c>
+      <c r="I23" s="13">
+        <v>30.949524270000001</v>
+      </c>
+      <c r="J23">
+        <v>-0.46285562499999999</v>
+      </c>
+      <c r="K23">
+        <v>0.78825855300000003</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24" s="13">
+        <v>5.1823334040000004</v>
+      </c>
+      <c r="E24" s="12">
+        <v>18.711380139999999</v>
+      </c>
+      <c r="F24" s="13">
+        <v>1.1285106090000001</v>
+      </c>
+      <c r="G24">
+        <v>24.987148120000001</v>
+      </c>
+      <c r="H24" s="13">
+        <v>0.46043980499999998</v>
+      </c>
+      <c r="I24" s="13">
+        <v>29.987806639999999</v>
+      </c>
+      <c r="J24">
+        <v>7.1441239029999997</v>
+      </c>
+      <c r="K24">
+        <v>0.81001934799999997</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>5.1482869367792903</v>
+      </c>
+      <c r="E25">
+        <v>15.835044158128801</v>
+      </c>
+      <c r="F25" s="15">
+        <v>1.1244094454515099</v>
+      </c>
+      <c r="G25">
+        <v>23.1174271692107</v>
+      </c>
+      <c r="H25" s="15">
+        <v>0.45961216642442498</v>
+      </c>
+      <c r="I25" s="15">
+        <v>29.111208619908201</v>
+      </c>
+      <c r="J25">
+        <v>1.4728076194878099</v>
+      </c>
+      <c r="K25">
+        <v>0.79372266328449603</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>10</v>
+      </c>
+      <c r="B26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26" s="13">
+        <v>5.1755467060000004</v>
+      </c>
+      <c r="E26" s="12">
+        <v>18.116868790000002</v>
+      </c>
+      <c r="F26" s="13">
+        <v>1.1348238129999999</v>
+      </c>
+      <c r="G26">
+        <v>28.633791110000001</v>
+      </c>
+      <c r="H26" s="13">
+        <v>0.46619514699999998</v>
+      </c>
+      <c r="I26" s="13">
+        <v>40.0745121</v>
+      </c>
+      <c r="J26">
+        <v>3.0910263379999998</v>
+      </c>
+      <c r="K26">
+        <v>0.79842427599999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27" s="13">
+        <v>5.3051976759999997</v>
+      </c>
+      <c r="E27" s="12">
+        <v>33.128009290000001</v>
+      </c>
+      <c r="F27" s="13">
+        <v>1.2083411369999999</v>
+      </c>
+      <c r="G27">
+        <v>81.360565600000001</v>
+      </c>
+      <c r="H27" s="13">
+        <v>0.51586884899999996</v>
+      </c>
+      <c r="I27" s="13">
+        <v>164.08104309999999</v>
+      </c>
+      <c r="J27">
+        <v>1.304060145</v>
+      </c>
+      <c r="K27">
+        <v>0.79301345300000003</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28" s="13">
+        <v>5.1756637650000004</v>
+      </c>
+      <c r="E28" s="12">
+        <v>17.85055715</v>
+      </c>
+      <c r="F28" s="13">
+        <v>1.130386648</v>
+      </c>
+      <c r="G28">
+        <v>25.60012553</v>
+      </c>
+      <c r="H28" s="13">
+        <v>0.46253652000000001</v>
+      </c>
+      <c r="I28" s="13">
+        <v>32.824176229999999</v>
+      </c>
+      <c r="J28">
+        <v>4.2508096210000001</v>
+      </c>
+      <c r="K28">
+        <v>0.80187562099999998</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>86</v>
+      </c>
+      <c r="B29" t="s">
+        <v>30</v>
+      </c>
+      <c r="D29" s="15">
+        <v>5.0725826731804204</v>
+      </c>
+      <c r="E29">
+        <v>29.823509196133301</v>
+      </c>
+      <c r="F29" s="15">
+        <v>1.1081362508291801</v>
+      </c>
+      <c r="G29">
+        <v>43.116454250674302</v>
+      </c>
+      <c r="H29" s="15">
+        <v>0.45332284366550502</v>
+      </c>
+      <c r="I29" s="15">
+        <v>48.172775998924898</v>
+      </c>
+      <c r="J29">
+        <v>8.4505067564480001</v>
+      </c>
+      <c r="K29">
+        <v>0.77221661699999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>87</v>
+      </c>
+      <c r="B30" t="s">
+        <v>32</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30" s="13">
+        <v>5.1996172930000002</v>
+      </c>
+      <c r="E30" s="12">
+        <v>20.97024313</v>
+      </c>
+      <c r="F30" s="13">
+        <v>1.1320706599999999</v>
+      </c>
+      <c r="G30">
+        <v>27.82413468</v>
+      </c>
+      <c r="H30" s="13">
+        <v>0.462307038</v>
+      </c>
+      <c r="I30" s="13">
+        <v>34.255471919999998</v>
+      </c>
+      <c r="J30">
+        <v>11.37092958</v>
+      </c>
+      <c r="K30">
+        <v>1.034252189</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K31">
+        <v>0.79572708115977397</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K32">
+        <v>0.82074704499999995</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>25</v>
+      </c>
+      <c r="B34" t="s">
+        <v>31</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34" s="13">
+        <v>5.1707489390000001</v>
+      </c>
+      <c r="E34" s="12">
+        <v>10.3553224</v>
+      </c>
+      <c r="F34" s="13">
+        <v>1.13540489</v>
+      </c>
+      <c r="G34">
+        <v>17.558327760000001</v>
+      </c>
+      <c r="H34" s="13">
+        <v>0.46694231400000002</v>
+      </c>
+      <c r="I34" s="13">
+        <v>25.800721169999999</v>
+      </c>
+      <c r="J34">
+        <v>-3.299558598</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>26</v>
+      </c>
+      <c r="B35" t="s">
+        <v>33</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35" s="13">
+        <v>5.4085868460000004</v>
+      </c>
+      <c r="E35" s="12">
+        <v>12.77316897</v>
+      </c>
+      <c r="F35" s="13">
+        <v>1.1700898660000001</v>
+      </c>
+      <c r="G35">
+        <v>17.155655410000001</v>
+      </c>
+      <c r="H35" s="13">
+        <v>0.478786141</v>
+      </c>
+      <c r="I35" s="13">
+        <v>24.32157226</v>
+      </c>
+      <c r="J35">
+        <v>23.65954266</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D5:D12 D14:D16 D18:D30 D34:D35 D3 H5:I12 H14:I16 H18:I30 H34:I35 H3:I3 F5:F12 F14:F16 F18:F30 F34:F35 F3">
+    <cfRule type="colorScale" priority="40">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="max"/>
+        <color rgb="FF00B050"/>
+        <color theme="0"/>
+        <color rgb="FFC00000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5:E12 E14:E16 E18:E30 E34:E35 E3">
+    <cfRule type="colorScale" priority="46">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="max"/>
+        <color rgb="FF00B050"/>
+        <color theme="0"/>
+        <color rgb="FFC00000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S4:Z4 AB4:AD4 AF4:AT4 Q4 S8:Z9 AB8:AD9 AF8:AT9 Q8:Q9 S6:Z6 AB6:AD6 AF6:AT6 Q6">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="max"/>
+        <color rgb="FF00B050"/>
+        <color theme="0"/>
+        <color rgb="FFC00000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S5:Z5 AB5:AD5 AF5:AT5 Q5">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="max"/>
+        <color rgb="FF00B050"/>
+        <color theme="0"/>
+        <color rgb="FFC00000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>